--- a/ig/ch-epl/CodeSystem-ch-epl-foph-type-of-price-change.xlsx
+++ b/ig/ch-epl/CodeSystem-ch-epl-foph-type-of-price-change.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T12:35:50+00:00</t>
+    <t>2026-04-07T14:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>13</t>
+    <t>18</t>
   </si>
   <si>
     <t>Level</t>
@@ -168,55 +168,85 @@
     <t>756002006005</t>
   </si>
   <si>
+    <t>Price reduction 18 months after SL listing</t>
+  </si>
+  <si>
+    <t>756002006006</t>
+  </si>
+  <si>
+    <t>Review of economic efficiency 1 year after SL listing</t>
+  </si>
+  <si>
+    <t>756002006007</t>
+  </si>
+  <si>
+    <t>Review of economic efficiency 2 years after SL listing</t>
+  </si>
+  <si>
+    <t>756002006008</t>
+  </si>
+  <si>
     <t>VAT-change</t>
   </si>
   <si>
-    <t>756002006006</t>
+    <t>756002006009</t>
   </si>
   <si>
     <t>Normal price mutation</t>
   </si>
   <si>
-    <t>756002006007</t>
+    <t>756002006010</t>
   </si>
   <si>
     <t>Price mutation after triennal review of pharmaceuticals</t>
   </si>
   <si>
-    <t>756002006008</t>
+    <t>756002006011</t>
   </si>
   <si>
     <t>Price mutation after patent expiry</t>
   </si>
   <si>
-    <t>756002006009</t>
+    <t>756002006012</t>
   </si>
   <si>
     <t>Price increase</t>
   </si>
   <si>
-    <t>756002006010</t>
+    <t>756002006013</t>
   </si>
   <si>
     <t>Price mutation at first listing</t>
   </si>
   <si>
-    <t>756002006011</t>
+    <t>756002006014</t>
   </si>
   <si>
     <t>Price mutation introduction of uniform wholesale margin</t>
   </si>
   <si>
-    <t>756002006012</t>
+    <t>756002006015</t>
   </si>
   <si>
     <t>Price mutation wholesale margin</t>
   </si>
   <si>
-    <t>756002006013</t>
+    <t>756002006016</t>
   </si>
   <si>
     <t>Price mutation uniform wholesale margin</t>
+  </si>
+  <si>
+    <t>756002006017</t>
+  </si>
+  <si>
+    <t>Change of dispensing category</t>
+  </si>
+  <si>
+    <t>756002006018</t>
+  </si>
+  <si>
+    <t>Health Technology Assessment</t>
   </si>
 </sst>
 </file>
@@ -528,7 +558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -701,6 +731,66 @@
       </c>
       <c r="D14" s="2"/>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
